--- a/cucumber-for-appian/src/test/resources/testdata/Regression/05_SMB_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/Regression/05_SMB_Regression.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="217">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -386,58 +386,91 @@
     <t>TC001</t>
   </si>
   <si>
-    <t>The Trustee for AKA Trust</t>
+    <t>SINGH, JATINDER</t>
   </si>
   <si>
     <t>Tier A</t>
   </si>
   <si>
-    <t>Trust</t>
-  </si>
-  <si>
-    <t>Medical, Office or Other Business Equipment</t>
+    <t>Sole Trader</t>
+  </si>
+  <si>
+    <t>Medium/Heavy Transport Vehicle</t>
   </si>
   <si>
     <t>YES</t>
   </si>
   <si>
-    <t>Used</t>
+    <t>Dealer</t>
+  </si>
+  <si>
+    <t>Finance Lease without Services</t>
+  </si>
+  <si>
+    <t>Caravans</t>
+  </si>
+  <si>
+    <t>Toyota Hatch</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
+    <t>$56,000</t>
+  </si>
+  <si>
+    <t>$1,500</t>
+  </si>
+  <si>
+    <t>$1,000</t>
+  </si>
+  <si>
+    <t>monthly in advance</t>
+  </si>
+  <si>
+    <t>Fuel Card</t>
+  </si>
+  <si>
+    <t>60 months</t>
+  </si>
+  <si>
+    <t>TOYOTA</t>
+  </si>
+  <si>
+    <t>BZ4X</t>
+  </si>
+  <si>
+    <t>71kWh AWD</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Finance Lease without Services</t>
-  </si>
-  <si>
-    <t>Telephone systems</t>
-  </si>
-  <si>
-    <t>$250,000</t>
-  </si>
-  <si>
-    <t>$1,500</t>
-  </si>
-  <si>
-    <t>$500</t>
-  </si>
-  <si>
-    <t>monthly in Arrears</t>
-  </si>
-  <si>
-    <t>48 months</t>
-  </si>
-  <si>
-    <t>45 Malonga Ave, Kellyville NSW 2155</t>
-  </si>
-  <si>
-    <t>A AGRICULTURE, FORESTRY AND FISHING</t>
-  </si>
-  <si>
-    <t>012 Mushroom and Vegetable Growing</t>
+    <t>AUDIA1VIN12345678</t>
+  </si>
+  <si>
+    <t>AUDIA1REG123456</t>
+  </si>
+  <si>
+    <t>TOYOTAENG123456</t>
+  </si>
+  <si>
+    <t>Comments: TOYOTA Passenger cars including electric vehicles</t>
+  </si>
+  <si>
+    <t>New Application[2]</t>
+  </si>
+  <si>
+    <t>WD HOMES SERVICES</t>
+  </si>
+  <si>
+    <t>56 Kimbler Rd, Roma QLD 4455</t>
+  </si>
+  <si>
+    <t>C MANUFACTURING</t>
+  </si>
+  <si>
+    <t>113 Dairy Product Manufacturing</t>
   </si>
   <si>
     <t>DAIRY PRODUCTS</t>
@@ -446,123 +479,88 @@
     <t>DAIRY PRODUCT ADVERTISEMENT</t>
   </si>
   <si>
+    <t>Dean</t>
+  </si>
+  <si>
+    <t>Jensen</t>
+  </si>
+  <si>
+    <t>Winchester</t>
+  </si>
+  <si>
+    <t>NZ Citizen</t>
+  </si>
+  <si>
+    <t>27/05/1981</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Renting</t>
+  </si>
+  <si>
+    <t>chandu.nagu+60@gmail.com</t>
+  </si>
+  <si>
+    <t>Learners Permit</t>
+  </si>
+  <si>
+    <t>Car Licence (C)</t>
+  </si>
+  <si>
+    <t>QLD</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
+    <t>YES, I DO HAVE SUFFICIENT ONGOING MONTHLY CASHFLOW TO MEET MY REPAYMENTS UNDER THIS FACILITY.</t>
+  </si>
+  <si>
+    <t>Select All Privacy Consent check boxes</t>
+  </si>
+  <si>
+    <t>C:\Users\HP\Downloads\Rental_Agreement_Document.pdf</t>
+  </si>
+  <si>
     <t>C:\Users\HP\Downloads\DealerQuote.pdf</t>
   </si>
   <si>
+    <t>APP-771</t>
+  </si>
+  <si>
+    <t>SMB-00001127
+SMB-00001127</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>02 Apr 2026 05:20 AM</t>
+  </si>
+  <si>
+    <t>Automation Introducer</t>
+  </si>
+  <si>
     <t>TC002</t>
   </si>
   <si>
-    <t>SINGH, JATINDER</t>
-  </si>
-  <si>
-    <t>Sole Trader</t>
-  </si>
-  <si>
     <t>Passenger or Light Commercial Vehicle</t>
   </si>
   <si>
-    <t>Yes, it is for a new asset</t>
-  </si>
-  <si>
-    <t>Chattel Mortgage</t>
-  </si>
-  <si>
-    <t>Passenger cars including electric vehicles</t>
-  </si>
-  <si>
-    <t>Toyota Hatch</t>
-  </si>
-  <si>
-    <t>$56,000</t>
-  </si>
-  <si>
-    <t>$0.00</t>
-  </si>
-  <si>
-    <t>$1,000</t>
+    <t>$1,500.00</t>
   </si>
   <si>
     <t>Monthly in Advance</t>
   </si>
   <si>
-    <t>Fuel Card</t>
-  </si>
-  <si>
-    <t>36 Months</t>
-  </si>
-  <si>
-    <t>TOYOTA</t>
-  </si>
-  <si>
-    <t>BZ4X</t>
-  </si>
-  <si>
-    <t>71kWh AWD</t>
-  </si>
-  <si>
     <t>TOYOTAVIN12345678</t>
   </si>
   <si>
     <t>TOYOTAREG123456</t>
   </si>
   <si>
-    <t>TOYOTAENG123456</t>
-  </si>
-  <si>
-    <t>Comments: TOYOTA Passenger cars including electric vehicles</t>
-  </si>
-  <si>
-    <t>New Application[2]</t>
-  </si>
-  <si>
-    <t>WD HOMES SERVICES</t>
-  </si>
-  <si>
-    <t>56 Kimbler Rd, Roma QLD 4455</t>
-  </si>
-  <si>
-    <t>C MANUFACTURING</t>
-  </si>
-  <si>
-    <t>113 Dairy Product Manufacturing</t>
-  </si>
-  <si>
-    <t>Dean</t>
-  </si>
-  <si>
-    <t>Jensen</t>
-  </si>
-  <si>
-    <t>Winchester</t>
-  </si>
-  <si>
-    <t>NZ Citizen</t>
-  </si>
-  <si>
-    <t>27/05/1981</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Renting</t>
-  </si>
-  <si>
-    <t>chandu.nagu+60@gmail.com</t>
-  </si>
-  <si>
-    <t>Learners Permit</t>
-  </si>
-  <si>
-    <t>Car Licence (C)</t>
-  </si>
-  <si>
-    <t>QLD</t>
-  </si>
-  <si>
     <t>$30,000</t>
   </si>
   <si>
@@ -572,9 +570,6 @@
     <t>$2,000</t>
   </si>
   <si>
-    <t>Select All Privacy Consent check boxes</t>
-  </si>
-  <si>
     <t>${TC001.Application Number}</t>
   </si>
   <si>
@@ -602,6 +597,9 @@
     <t>$68,122.30</t>
   </si>
   <si>
+    <t>$76,961.17</t>
+  </si>
+  <si>
     <t>$1,420.12</t>
   </si>
   <si>
@@ -611,10 +609,10 @@
     <t>Dealer Pricing</t>
   </si>
   <si>
-    <t>$0.50</t>
-  </si>
-  <si>
-    <t>2.68%</t>
+    <t>$114.61</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>30.00%</t>
@@ -665,45 +663,18 @@
     <t>TC003</t>
   </si>
   <si>
-    <t>Ebony</t>
-  </si>
-  <si>
-    <t>Grey Synthetic leather</t>
-  </si>
-  <si>
-    <t>monthly in advance</t>
-  </si>
-  <si>
-    <t>Roadside Assistance</t>
-  </si>
-  <si>
-    <t>NSW</t>
-  </si>
-  <si>
-    <t>$10,000.00</t>
-  </si>
-  <si>
-    <t>AUDIA1VIN12345678</t>
-  </si>
-  <si>
-    <t>AUDIA1REG123456</t>
-  </si>
-  <si>
-    <t>YES, I DO HAVE SUFFICIENT ONGOING MONTHLY CASHFLOW TO MEET MY REPAYMENTS UNDER THIS FACILITY.</t>
-  </si>
-  <si>
-    <t>C:\Users\HP\Downloads\Rental_Agreement_Document.pdf</t>
+    <t>Buses and coaches</t>
+  </si>
+  <si>
+    <t>$200,000</t>
+  </si>
+  <si>
+    <t>Monthly in Arrears</t>
   </si>
   <si>
     <t>TC004</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Dealer</t>
-  </si>
-  <si>
     <t>71KWH AWD</t>
   </si>
   <si>
@@ -722,13 +693,13 @@
     <t>$72,053.37</t>
   </si>
   <si>
-    <t>$671,875.80</t>
-  </si>
-  <si>
     <t>$1,145.61</t>
   </si>
   <si>
     <t>$15,524.74</t>
+  </si>
+  <si>
+    <t>2.68%</t>
   </si>
   <si>
     <t>54.32%</t>
@@ -1426,7 +1397,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1465,9 +1436,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2270,7 +2238,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="72" spans="1:119">
+    <row r="2" s="2" customFormat="1" ht="84" spans="1:95">
       <c r="A2" s="8" t="s">
         <v>117</v>
       </c>
@@ -2278,7 +2246,7 @@
         <v>118</v>
       </c>
       <c r="C2" s="9">
-        <v>86695778963</v>
+        <v>39008846636</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>119</v>
@@ -2289,46 +2257,48 @@
       <c r="F2" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="9"/>
+      <c r="J2" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9"/>
+      <c r="M2" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="O2" s="9"/>
+      <c r="P2" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="Q2" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="R2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="S2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="U2" s="9" t="s">
         <v>128</v>
       </c>
       <c r="V2" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="W2" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="W2" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="X2" s="9" t="s">
         <v>130</v>
@@ -2339,8 +2309,8 @@
       <c r="Z2" s="8">
         <v>30</v>
       </c>
-      <c r="AA2" s="12" t="s">
-        <v>124</v>
+      <c r="AA2" s="12">
+        <v>0</v>
       </c>
       <c r="AB2" s="12"/>
       <c r="AC2" s="12"/>
@@ -2354,142 +2324,171 @@
         <v>131</v>
       </c>
       <c r="AK2" s="9" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AL2" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AN2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AO2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="AP2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="AQ2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="AR2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
+      </c>
+      <c r="AP2" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="AR2" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="AS2" s="9"/>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
-      <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
-      <c r="AY2" s="9"/>
-      <c r="AZ2" s="9"/>
-      <c r="BA2" s="9"/>
-      <c r="BB2" s="9"/>
-      <c r="BC2" s="9"/>
+      <c r="AV2" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW2" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX2" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AY2" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="AZ2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB2" s="9">
+        <v>39008846636</v>
+      </c>
+      <c r="BC2" s="9" t="s">
+        <v>143</v>
+      </c>
       <c r="BD2" s="9"/>
       <c r="BE2" s="9" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="BF2" s="9" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="BG2" s="9" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="BH2" s="9" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="BI2" s="9" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="BJ2" s="9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="BK2" s="9" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="BL2" s="9" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="BM2" s="9" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="BN2" s="14" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="BO2" s="9" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="BP2" s="9" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="BQ2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="BR2" s="9" t="s">
-        <v>124</v>
+        <v>144</v>
+      </c>
+      <c r="BR2" s="9">
+        <v>411203205</v>
       </c>
       <c r="BS2" s="9" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="BT2" s="9" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="BU2" s="9" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="BV2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="BW2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="BX2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="BZ2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="CA2" s="9"/>
+        <v>159</v>
+      </c>
+      <c r="BW2" s="9">
+        <v>13501975</v>
+      </c>
+      <c r="BX2" s="9"/>
+      <c r="BY2" s="9"/>
+      <c r="BZ2" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA2" s="13" t="s">
+        <v>161</v>
+      </c>
       <c r="CB2" s="9" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="CC2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CD2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CE2" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CF2" s="9"/>
       <c r="CG2" s="9"/>
       <c r="CH2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>139</v>
+        <v>162</v>
+      </c>
+      <c r="CI2" s="9" t="s">
+        <v>163</v>
       </c>
       <c r="CJ2" s="9"/>
       <c r="CK2" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="DO2" s="9" t="s">
-        <v>123</v>
+        <v>164</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>165</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>167</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>168</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" ht="84" spans="1:120">
       <c r="A3" s="8" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C3" s="9">
         <v>39008846636</v>
@@ -2498,52 +2497,50 @@
         <v>119</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G3" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8" t="s">
-        <v>144</v>
-      </c>
+      <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>146</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="8" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
       <c r="U3" s="8" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="V3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="W3" s="8" t="s">
-        <v>149</v>
+      <c r="W3" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="Y3" s="8">
         <v>5</v>
@@ -2561,227 +2558,229 @@
       <c r="AH3" s="8"/>
       <c r="AI3" s="8"/>
       <c r="AJ3" s="8" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AK3" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL3" s="8" t="s">
-        <v>153</v>
+        <v>132</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="AM3" s="8"/>
       <c r="AN3" s="8"/>
       <c r="AO3" s="8"/>
       <c r="AP3" s="8" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="AQ3" s="8" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="AR3" s="8" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="AS3" s="8"/>
       <c r="AT3" s="8"/>
       <c r="AU3" s="8"/>
       <c r="AV3" s="8" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="AW3" s="8" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="AX3" s="8" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="AY3" s="8" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="AZ3" s="8" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="BA3" s="8" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="BB3" s="9">
         <v>39008846636</v>
       </c>
       <c r="BC3" s="9" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="BD3" s="8"/>
       <c r="BE3" s="9" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="BF3" s="9" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="BG3" s="9" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="BH3" s="9" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="BI3" s="9" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="BJ3" s="9" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="BK3" s="9" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="BL3" s="9" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="BM3" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="BN3" s="15" t="s">
-        <v>170</v>
+        <v>152</v>
+      </c>
+      <c r="BN3" s="14" t="s">
+        <v>153</v>
       </c>
       <c r="BO3" s="9" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="BP3" s="9" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="BQ3" s="9" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="BR3" s="9">
         <v>411203205</v>
       </c>
       <c r="BS3" s="9" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="BT3" s="9" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="BU3" s="9" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="BV3" s="9" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="BW3" s="9">
         <v>13501975</v>
       </c>
       <c r="BX3" s="8" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="BY3" s="8" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="BZ3" s="8" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="CA3" s="8"/>
       <c r="CB3" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="CC3" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="CC3" s="8" t="s">
+      <c r="CD3" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="CD3" s="8" t="s">
-        <v>179</v>
-      </c>
       <c r="CE3" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="CF3" s="8"/>
       <c r="CG3" s="8"/>
       <c r="CH3" s="8" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="CI3" s="8"/>
       <c r="CJ3" s="8"/>
       <c r="CK3" s="8"/>
       <c r="CL3" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="CM3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="CN3" s="8" t="s">
         <v>181</v>
-      </c>
-      <c r="CM3" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="CN3" s="8" t="s">
-        <v>183</v>
       </c>
       <c r="CO3" s="8"/>
       <c r="CP3" s="8"/>
       <c r="CQ3" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="CR3" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="CR3" s="8" t="s">
+      <c r="CT3" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="CS3" s="8" t="s">
+      <c r="CU3" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="CT3" s="18" t="s">
+      <c r="CV3" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="CU3" s="18" t="s">
+      <c r="CW3" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="CV3" s="18" t="s">
+      <c r="CX3" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="CW3" s="18"/>
-      <c r="CX3" s="18" t="s">
+      <c r="CY3" s="17"/>
+      <c r="CZ3" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="DA3" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB3" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="CY3" s="18"/>
-      <c r="CZ3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="DA3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="DB3" s="18" t="s">
+      <c r="DC3" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="DC3" s="18" t="s">
+      <c r="DD3" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="DE3" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="DD3" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="DE3" s="18" t="s">
+      <c r="DF3" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="DF3" s="18" t="s">
+      <c r="DG3" s="17"/>
+      <c r="DH3" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="DG3" s="18"/>
-      <c r="DH3" s="18" t="s">
+      <c r="DI3" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="DI3" s="18" t="s">
+      <c r="DJ3" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="DJ3" s="18" t="s">
+      <c r="DK3" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="DL3" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="DK3" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="DL3" s="18" t="s">
+      <c r="DM3" s="17"/>
+      <c r="DN3" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="DM3" s="18"/>
-      <c r="DN3" s="18" t="s">
+      <c r="DO3" s="17"/>
+      <c r="DP3" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="DO3" s="18"/>
-      <c r="DP3" s="8" t="s">
+    </row>
+    <row r="4" s="2" customFormat="1" ht="84" spans="1:89">
+      <c r="A4" s="8" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="72" spans="1:89">
-      <c r="A4" s="8" t="s">
-        <v>201</v>
-      </c>
       <c r="B4" s="9" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C4" s="9">
         <v>39008846636</v>
@@ -2790,56 +2789,58 @@
         <v>119</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="J4" s="9"/>
       <c r="K4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="M4" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M4" s="9" t="s">
+      <c r="N4" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="8" t="s">
+        <v>126</v>
+      </c>
       <c r="R4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="U4" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="S4" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="T4" s="9">
-        <v>10000</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>148</v>
-      </c>
       <c r="V4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="W4" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="W4" s="8" t="s">
-        <v>149</v>
-      </c>
       <c r="X4" s="9" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="Y4" s="8">
         <v>5</v>
@@ -2847,121 +2848,125 @@
       <c r="Z4" s="8">
         <v>30</v>
       </c>
-      <c r="AA4" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="9"/>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
+      <c r="AA4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="12"/>
       <c r="AJ4" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AK4" s="9" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="AL4" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM4" s="9" t="s">
-        <v>206</v>
+        <v>127</v>
       </c>
       <c r="AN4" s="9" t="s">
-        <v>207</v>
+        <v>127</v>
       </c>
       <c r="AO4" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="AP4" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="AQ4" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="AR4" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
+      </c>
+      <c r="AP4" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ4" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="AR4" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="AS4" s="9"/>
       <c r="AT4" s="9"/>
       <c r="AU4" s="9"/>
       <c r="AV4" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW4" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX4" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="AW4" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="AX4" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="AY4" s="9"/>
-      <c r="AZ4" s="9"/>
-      <c r="BA4" s="9" t="s">
-        <v>161</v>
+      <c r="AY4" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="AZ4" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA4" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="BB4" s="9">
         <v>39008846636</v>
       </c>
       <c r="BC4" s="9" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="BD4" s="9"/>
       <c r="BE4" s="9" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="BF4" s="9" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="BG4" s="9" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="BH4" s="9" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="BI4" s="9" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="BJ4" s="9" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="BK4" s="9" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="BL4" s="9" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="BM4" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="BN4" s="15" t="s">
-        <v>170</v>
+        <v>152</v>
+      </c>
+      <c r="BN4" s="14" t="s">
+        <v>153</v>
       </c>
       <c r="BO4" s="9" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="BP4" s="9" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="BQ4" s="9" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="BR4" s="9">
         <v>411203205</v>
       </c>
       <c r="BS4" s="9" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="BT4" s="9" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="BU4" s="9" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="BV4" s="9" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="BW4" s="9">
         <v>13501975</v>
@@ -2969,42 +2974,42 @@
       <c r="BX4" s="9"/>
       <c r="BY4" s="9"/>
       <c r="BZ4" s="13" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="CA4" s="13" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="CB4" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CC4" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CD4" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CE4" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CF4" s="9"/>
       <c r="CG4" s="9"/>
       <c r="CH4" s="9" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="CI4" s="9" t="s">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="CJ4" s="9"/>
       <c r="CK4" s="2" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" s="4" customFormat="1" ht="129" customHeight="1" spans="1:120">
       <c r="A5" s="8" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C5" s="9">
         <v>39008846636</v>
@@ -3013,56 +3018,52 @@
         <v>119</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>213</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="G5" s="9"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
-        <v>144</v>
-      </c>
+      <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9" t="s">
-        <v>214</v>
+        <v>123</v>
       </c>
       <c r="L5" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="M5" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="N5" s="9" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="8" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="S5" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="V5" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="W5" s="8" t="s">
-        <v>149</v>
+      <c r="W5" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="X5" s="9" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="Y5" s="8">
         <v>5</v>
@@ -3071,7 +3072,7 @@
         <v>30</v>
       </c>
       <c r="AA5" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AB5" s="13"/>
       <c r="AC5" s="13"/>
@@ -3082,43 +3083,43 @@
       <c r="AH5" s="13"/>
       <c r="AI5" s="13"/>
       <c r="AJ5" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AK5" s="9" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="AL5" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AM5" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AN5" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AO5" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AP5" s="9" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="AQ5" s="9" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="AR5" s="9" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="AS5" s="9"/>
       <c r="AT5" s="9"/>
       <c r="AU5" s="9"/>
       <c r="AV5" s="9" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="AW5" s="9" t="s">
-        <v>208</v>
+        <v>138</v>
       </c>
       <c r="AX5" s="9" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="AY5" s="9"/>
       <c r="AZ5" s="9"/>
@@ -3127,62 +3128,62 @@
         <v>39008846636</v>
       </c>
       <c r="BC5" s="9" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="BD5" s="9"/>
       <c r="BE5" s="9" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="BF5" s="9" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="BG5" s="9" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="BH5" s="9" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="BI5" s="9" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="BJ5" s="9" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="BK5" s="9" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="BL5" s="9" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="BM5" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="BN5" s="15" t="s">
-        <v>170</v>
+        <v>152</v>
+      </c>
+      <c r="BN5" s="14" t="s">
+        <v>153</v>
       </c>
       <c r="BO5" s="9" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="BP5" s="9" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="BQ5" s="9" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="BR5" s="9">
         <v>411203205</v>
       </c>
       <c r="BS5" s="9" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="BT5" s="9" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="BU5" s="9" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="BV5" s="9" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="BW5" s="9">
         <v>13501975</v>
@@ -3190,111 +3191,111 @@
       <c r="BX5" s="9"/>
       <c r="BY5" s="9"/>
       <c r="BZ5" s="13" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="CA5" s="13" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="CB5" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CC5" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CD5" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CE5" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CF5" s="13"/>
       <c r="CG5" s="13"/>
       <c r="CH5" s="13" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="CI5" s="13"/>
       <c r="CJ5" s="13"/>
       <c r="CK5" s="8"/>
       <c r="CL5" s="8" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="CM5" s="8" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="CN5" s="8" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="CO5" s="8"/>
       <c r="CP5" s="8"/>
       <c r="CQ5" s="8" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="CR5" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS5" s="8"/>
+      <c r="CT5" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="CS5" s="8"/>
-      <c r="CT5" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="CU5" s="18" t="s">
+      <c r="CU5" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="CV5" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="CW5" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="CV5" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="CW5" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="CX5" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="CY5" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="CZ5" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="DA5" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="DB5" s="18" t="s">
+      <c r="CX5" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="CY5" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="CZ5" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="DA5" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB5" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="DC5" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="DC5" s="18" t="s">
+      <c r="DD5" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="DE5" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="DD5" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="DE5" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="DF5" s="18" t="s">
+      <c r="DF5" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="DG5" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="DH5" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="DG5" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="DH5" s="18" t="s">
+      <c r="DI5" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="DI5" s="18" t="s">
+      <c r="DJ5" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="DJ5" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="DK5" s="18"/>
-      <c r="DL5" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM5" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="DN5" s="18"/>
-      <c r="DO5" s="18"/>
+      <c r="DK5" s="17"/>
+      <c r="DL5" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="DM5" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="DN5" s="17"/>
+      <c r="DO5" s="17"/>
       <c r="DP5" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:120">
@@ -3363,11 +3364,11 @@
       <c r="BK6" s="8"/>
       <c r="BL6" s="8"/>
       <c r="BM6" s="8"/>
-      <c r="BN6" s="16"/>
+      <c r="BN6" s="15"/>
       <c r="BO6" s="8"/>
       <c r="BP6" s="8"/>
       <c r="BQ6" s="8"/>
-      <c r="BR6" s="17"/>
+      <c r="BR6" s="16"/>
       <c r="BS6" s="8"/>
       <c r="BT6" s="8"/>
       <c r="BU6" s="13"/>
@@ -3395,28 +3396,28 @@
       <c r="CQ6" s="8"/>
       <c r="CR6" s="8"/>
       <c r="CS6" s="8"/>
-      <c r="CT6" s="18"/>
-      <c r="CU6" s="18"/>
-      <c r="CV6" s="18"/>
-      <c r="CW6" s="18"/>
-      <c r="CX6" s="18"/>
-      <c r="CY6" s="18"/>
-      <c r="CZ6" s="18"/>
-      <c r="DA6" s="18"/>
-      <c r="DB6" s="18"/>
-      <c r="DC6" s="18"/>
-      <c r="DD6" s="18"/>
-      <c r="DE6" s="18"/>
-      <c r="DF6" s="18"/>
-      <c r="DG6" s="18"/>
-      <c r="DH6" s="18"/>
-      <c r="DI6" s="18"/>
-      <c r="DJ6" s="18"/>
-      <c r="DK6" s="18"/>
-      <c r="DL6" s="18"/>
-      <c r="DM6" s="18"/>
-      <c r="DN6" s="18"/>
-      <c r="DO6" s="18"/>
+      <c r="CT6" s="17"/>
+      <c r="CU6" s="17"/>
+      <c r="CV6" s="17"/>
+      <c r="CW6" s="17"/>
+      <c r="CX6" s="17"/>
+      <c r="CY6" s="17"/>
+      <c r="CZ6" s="17"/>
+      <c r="DA6" s="17"/>
+      <c r="DB6" s="17"/>
+      <c r="DC6" s="17"/>
+      <c r="DD6" s="17"/>
+      <c r="DE6" s="17"/>
+      <c r="DF6" s="17"/>
+      <c r="DG6" s="17"/>
+      <c r="DH6" s="17"/>
+      <c r="DI6" s="17"/>
+      <c r="DJ6" s="17"/>
+      <c r="DK6" s="17"/>
+      <c r="DL6" s="17"/>
+      <c r="DM6" s="17"/>
+      <c r="DN6" s="17"/>
+      <c r="DO6" s="17"/>
       <c r="DP6" s="8"/>
     </row>
     <row r="7" s="3" customFormat="1" spans="1:120">
@@ -3485,11 +3486,11 @@
       <c r="BK7" s="8"/>
       <c r="BL7" s="8"/>
       <c r="BM7" s="8"/>
-      <c r="BN7" s="16"/>
+      <c r="BN7" s="15"/>
       <c r="BO7" s="8"/>
       <c r="BP7" s="8"/>
       <c r="BQ7" s="8"/>
-      <c r="BR7" s="17"/>
+      <c r="BR7" s="16"/>
       <c r="BS7" s="8"/>
       <c r="BT7" s="8"/>
       <c r="BU7" s="13"/>
@@ -3607,11 +3608,11 @@
       <c r="BK8" s="8"/>
       <c r="BL8" s="8"/>
       <c r="BM8" s="8"/>
-      <c r="BN8" s="16"/>
+      <c r="BN8" s="15"/>
       <c r="BO8" s="8"/>
       <c r="BP8" s="8"/>
       <c r="BQ8" s="8"/>
-      <c r="BR8" s="17"/>
+      <c r="BR8" s="16"/>
       <c r="BS8" s="8"/>
       <c r="BT8" s="8"/>
       <c r="BU8" s="13"/>
@@ -5741,6 +5742,7 @@
   <hyperlinks>
     <hyperlink ref="BS3" r:id="rId1" display="chandu.nagu+60@gmail.com"/>
     <hyperlink ref="BS5" r:id="rId1" display="chandu.nagu+60@gmail.com"/>
+    <hyperlink ref="BS2" r:id="rId1" display="chandu.nagu+60@gmail.com"/>
     <hyperlink ref="BS4" r:id="rId1" display="chandu.nagu+60@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
